--- a/GoFAA0_Construccion/GoFAA00A_Plantillas_Basicas/0000B-EN0AA-000-000-TXT-000-000-SO_aux_hojaCalculo_es-WF-2600.xlsx
+++ b/GoFAA0_Construccion/GoFAA00A_Plantillas_Basicas/0000B-EN0AA-000-000-TXT-000-000-SO_aux_hojaCalculo_es-WF-2600.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jctorresce/Library/Mobile Documents/com~apple~CloudDocs/Workshop/PCoSA0000B_Empresa/GoFAA0_Construccion/GoFAA00A_Plantillas_Generales/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jctorresce/Library/Mobile Documents/com~apple~CloudDocs/Workshop/PCoSA0000B_Empresa/GoFAA0_Construccion/GoFAA00A_Plantillas_Basicas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B43260-FBF9-5A4C-B664-9F4C17D53DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04663F95-E48D-2449-BE69-F626498359BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29540" yWindow="500" windowWidth="20620" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -2772,6 +2770,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2787,10 +2791,79 @@
     <xf numFmtId="49" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="6" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2832,110 +2905,35 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="6" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="2" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3254,7 +3252,7 @@
           <a:effectLst/>
           <a:extLst>
             <a:ext uri="{C572A759-6A51-4108-AA02-DFA0A04FC94B}">
-              <ma14:wrappingTextBoxFlag xmlns:ma14="http://schemas.microsoft.com/office/mac/drawingml/2011/main" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="" val="1"/>
+              <ma14:wrappingTextBoxFlag xmlns="" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:ma14="http://schemas.microsoft.com/office/mac/drawingml/2011/main" val="1"/>
             </a:ext>
           </a:extLst>
         </xdr:spPr>
@@ -3678,7 +3676,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{C572A759-6A51-4108-AA02-DFA0A04FC94B}">
-            <ma14:wrappingTextBoxFlag xmlns:ma14="http://schemas.microsoft.com/office/mac/drawingml/2011/main" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="" val="1"/>
+            <ma14:wrappingTextBoxFlag xmlns="" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:ma14="http://schemas.microsoft.com/office/mac/drawingml/2011/main" val="1"/>
           </a:ext>
         </a:extLst>
       </xdr:spPr>
@@ -4716,12 +4714,12 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="CTDi Pro Org">
   <a:themeElements>
-    <a:clrScheme name="CTDi Pro Branding colors">
+    <a:clrScheme name="Custom 1">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFE"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="555555"/>
@@ -4730,22 +4728,22 @@
         <a:srgbClr val="AAAAAA"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="C61C00"/>
+        <a:srgbClr val="C60D00"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="FF5500"/>
+        <a:srgbClr val="FE5400"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FFAA38"/>
+        <a:srgbClr val="FEAA1C"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="00558E"/>
+        <a:srgbClr val="00548E"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="008EFF"/>
+        <a:srgbClr val="008DFF"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="71C6FF"/>
+        <a:srgbClr val="71C6FE"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="1C5571"/>
@@ -5917,17 +5915,17 @@
     <row r="1" spans="1:3" ht="28.25" customHeight="1">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="204"/>
+      <c r="C1" s="206"/>
     </row>
     <row r="2" spans="1:3" ht="14.25" customHeight="1">
       <c r="A2" s="15"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="205"/>
+      <c r="C2" s="207"/>
     </row>
     <row r="3" spans="1:3" ht="14.25" customHeight="1">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
-      <c r="C3" s="205"/>
+      <c r="C3" s="207"/>
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1">
       <c r="A4" s="15"/>
@@ -5966,11 +5964,11 @@
       <c r="C9" s="7"/>
     </row>
     <row r="10" spans="1:3" ht="19.75" customHeight="1">
-      <c r="A10" s="202" t="s">
+      <c r="A10" s="204" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="203"/>
-      <c r="C10" s="203"/>
+      <c r="B10" s="205"/>
+      <c r="C10" s="205"/>
     </row>
     <row r="11" spans="1:3" ht="14.25" customHeight="1">
       <c r="A11" s="19"/>
@@ -5990,7 +5988,7 @@
       <c r="C13" s="14"/>
     </row>
     <row r="14" spans="1:3" ht="28.25" customHeight="1">
-      <c r="A14" s="206" t="s">
+      <c r="A14" s="208" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="193"/>
@@ -6065,11 +6063,11 @@
     </row>
     <row r="29" spans="1:8" ht="120.5" customHeight="1">
       <c r="D29" s="31"/>
-      <c r="E29" s="207" t="s">
+      <c r="E29" s="202" t="s">
         <v>14</v>
       </c>
-      <c r="F29" s="208"/>
-      <c r="G29" s="208"/>
+      <c r="F29" s="203"/>
+      <c r="G29" s="203"/>
       <c r="H29" s="32"/>
     </row>
     <row r="30" spans="1:8" ht="10" customHeight="1">
@@ -6115,39 +6113,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.25" customHeight="1">
-      <c r="A1" s="214" t="s">
+      <c r="A1" s="239" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="215"/>
-      <c r="C1" s="216"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="204"/>
+      <c r="B1" s="240"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="206"/>
     </row>
     <row r="2" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A2" s="218" t="s">
+      <c r="A2" s="243" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="219"/>
-      <c r="C2" s="220"/>
-      <c r="D2" s="221"/>
-      <c r="E2" s="209"/>
+      <c r="B2" s="244"/>
+      <c r="C2" s="245"/>
+      <c r="D2" s="246"/>
+      <c r="E2" s="234"/>
     </row>
     <row r="3" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A3" s="210" t="s">
+      <c r="A3" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="211"/>
-      <c r="C3" s="211"/>
-      <c r="D3" s="211"/>
+      <c r="B3" s="236"/>
+      <c r="C3" s="236"/>
+      <c r="D3" s="236"/>
       <c r="E3" s="36" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A4" s="212"/>
-      <c r="B4" s="213"/>
-      <c r="C4" s="213"/>
-      <c r="D4" s="213"/>
+      <c r="A4" s="237"/>
+      <c r="B4" s="238"/>
+      <c r="C4" s="238"/>
+      <c r="D4" s="238"/>
       <c r="E4" s="37" t="s">
         <v>19</v>
       </c>
@@ -6192,70 +6190,70 @@
       <c r="E9" s="44"/>
     </row>
     <row r="10" spans="1:5" ht="85" customHeight="1">
-      <c r="A10" s="222" t="s">
+      <c r="A10" s="230" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="223"/>
-      <c r="C10" s="228" t="s">
+      <c r="B10" s="231"/>
+      <c r="C10" s="221" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="229"/>
-      <c r="E10" s="230"/>
+      <c r="D10" s="222"/>
+      <c r="E10" s="223"/>
     </row>
     <row r="11" spans="1:5" ht="42.5" customHeight="1">
-      <c r="A11" s="224" t="s">
+      <c r="A11" s="232" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="225"/>
-      <c r="C11" s="231" t="s">
+      <c r="B11" s="233"/>
+      <c r="C11" s="224" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="232"/>
-      <c r="E11" s="233"/>
+      <c r="D11" s="225"/>
+      <c r="E11" s="226"/>
     </row>
     <row r="12" spans="1:5" ht="42.5" customHeight="1">
-      <c r="A12" s="224" t="s">
+      <c r="A12" s="232" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="225"/>
-      <c r="C12" s="231" t="s">
+      <c r="B12" s="233"/>
+      <c r="C12" s="224" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="232"/>
-      <c r="E12" s="233"/>
+      <c r="D12" s="225"/>
+      <c r="E12" s="226"/>
     </row>
     <row r="13" spans="1:5" ht="42.5" customHeight="1">
-      <c r="A13" s="224" t="s">
+      <c r="A13" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="225"/>
-      <c r="C13" s="231" t="s">
+      <c r="B13" s="233"/>
+      <c r="C13" s="224" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="232"/>
-      <c r="E13" s="233"/>
+      <c r="D13" s="225"/>
+      <c r="E13" s="226"/>
     </row>
     <row r="14" spans="1:5" ht="42.5" customHeight="1">
-      <c r="A14" s="224" t="s">
+      <c r="A14" s="232" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="225"/>
-      <c r="C14" s="231" t="s">
+      <c r="B14" s="233"/>
+      <c r="C14" s="224" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="232"/>
-      <c r="E14" s="233"/>
+      <c r="D14" s="225"/>
+      <c r="E14" s="226"/>
     </row>
     <row r="15" spans="1:5" ht="85" customHeight="1">
-      <c r="A15" s="226" t="s">
+      <c r="A15" s="219" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="227"/>
-      <c r="C15" s="234" t="s">
+      <c r="B15" s="220"/>
+      <c r="C15" s="227" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="235"/>
-      <c r="E15" s="236"/>
+      <c r="D15" s="228"/>
+      <c r="E15" s="229"/>
     </row>
     <row r="16" spans="1:5" ht="10" customHeight="1">
       <c r="A16" s="45"/>
@@ -6284,11 +6282,11 @@
       <c r="A19" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="237" t="s">
+      <c r="B19" s="213" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="238"/>
-      <c r="D19" s="238"/>
+      <c r="C19" s="214"/>
+      <c r="D19" s="214"/>
       <c r="E19" s="50" t="s">
         <v>35</v>
       </c>
@@ -6297,41 +6295,41 @@
       <c r="A20" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="239" t="s">
+      <c r="B20" s="215" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="240"/>
-      <c r="D20" s="240"/>
+      <c r="C20" s="216"/>
+      <c r="D20" s="216"/>
       <c r="E20" s="52" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="17" customHeight="1">
       <c r="A21" s="53"/>
-      <c r="B21" s="241"/>
-      <c r="C21" s="242"/>
-      <c r="D21" s="242"/>
+      <c r="B21" s="217"/>
+      <c r="C21" s="218"/>
+      <c r="D21" s="218"/>
       <c r="E21" s="54"/>
     </row>
     <row r="22" spans="1:5" ht="17" customHeight="1">
       <c r="A22" s="53"/>
-      <c r="B22" s="241"/>
-      <c r="C22" s="242"/>
-      <c r="D22" s="242"/>
+      <c r="B22" s="217"/>
+      <c r="C22" s="218"/>
+      <c r="D22" s="218"/>
       <c r="E22" s="54"/>
     </row>
     <row r="23" spans="1:5" ht="17" customHeight="1">
       <c r="A23" s="53"/>
-      <c r="B23" s="241"/>
-      <c r="C23" s="242"/>
-      <c r="D23" s="242"/>
+      <c r="B23" s="217"/>
+      <c r="C23" s="218"/>
+      <c r="D23" s="218"/>
       <c r="E23" s="54"/>
     </row>
     <row r="24" spans="1:5" ht="17" customHeight="1">
       <c r="A24" s="55"/>
-      <c r="B24" s="243"/>
-      <c r="C24" s="244"/>
-      <c r="D24" s="244"/>
+      <c r="B24" s="209"/>
+      <c r="C24" s="210"/>
+      <c r="D24" s="210"/>
       <c r="E24" s="56"/>
     </row>
     <row r="25" spans="1:5" ht="28.25" customHeight="1">
@@ -6351,13 +6349,13 @@
       <c r="E26" s="59"/>
     </row>
     <row r="27" spans="1:5" ht="221" customHeight="1">
-      <c r="A27" s="245" t="s">
+      <c r="A27" s="211" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="246"/>
-      <c r="C27" s="246"/>
-      <c r="D27" s="246"/>
-      <c r="E27" s="246"/>
+      <c r="B27" s="212"/>
+      <c r="C27" s="212"/>
+      <c r="D27" s="212"/>
+      <c r="E27" s="212"/>
     </row>
     <row r="28" spans="1:5" ht="14.25" customHeight="1">
       <c r="A28" s="57" t="s">
@@ -6369,13 +6367,13 @@
       <c r="E28" s="59"/>
     </row>
     <row r="29" spans="1:5" ht="221" customHeight="1">
-      <c r="A29" s="245" t="s">
+      <c r="A29" s="211" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="246"/>
-      <c r="C29" s="246"/>
-      <c r="D29" s="246"/>
-      <c r="E29" s="246"/>
+      <c r="B29" s="212"/>
+      <c r="C29" s="212"/>
+      <c r="D29" s="212"/>
+      <c r="E29" s="212"/>
     </row>
     <row r="30" spans="1:5" ht="10" customHeight="1">
       <c r="A30" s="8"/>
@@ -6433,7 +6431,7 @@
       <c r="E36" s="14"/>
     </row>
     <row r="37" spans="1:5" ht="28.25" customHeight="1">
-      <c r="A37" s="206" t="s">
+      <c r="A37" s="208" t="s">
         <v>13</v>
       </c>
       <c r="B37" s="193"/>
@@ -6534,11 +6532,11 @@
     </row>
     <row r="52" spans="1:10" ht="120.5" customHeight="1">
       <c r="F52" s="31"/>
-      <c r="G52" s="207" t="s">
+      <c r="G52" s="202" t="s">
         <v>14</v>
       </c>
-      <c r="H52" s="208"/>
-      <c r="I52" s="208"/>
+      <c r="H52" s="203"/>
+      <c r="I52" s="203"/>
       <c r="J52" s="32"/>
     </row>
     <row r="53" spans="1:10" ht="10" customHeight="1">
@@ -6550,16 +6548,11 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A3:D4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="C11:E11"/>
@@ -6572,11 +6565,16 @@
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A3:D4"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="G52:I52"/>
   </mergeCells>
   <pageMargins left="0.59055100000000005" right="0.59055100000000005" top="0.39370100000000002" bottom="0.39370100000000002" header="0.19685" footer="0.39370100000000002"/>
   <pageSetup orientation="portrait"/>
@@ -6607,47 +6605,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.25" customHeight="1">
-      <c r="A1" s="214" t="s">
+      <c r="A1" s="239" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="215"/>
-      <c r="C1" s="215"/>
-      <c r="D1" s="215"/>
-      <c r="E1" s="215"/>
-      <c r="F1" s="216"/>
-      <c r="G1" s="204"/>
+      <c r="B1" s="240"/>
+      <c r="C1" s="240"/>
+      <c r="D1" s="240"/>
+      <c r="E1" s="240"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="206"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A2" s="218" t="s">
+      <c r="A2" s="243" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="219"/>
-      <c r="C2" s="220"/>
+      <c r="B2" s="244"/>
+      <c r="C2" s="245"/>
       <c r="D2" s="247"/>
       <c r="E2" s="247"/>
-      <c r="F2" s="221"/>
-      <c r="G2" s="209"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="234"/>
     </row>
     <row r="3" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A3" s="210" t="s">
+      <c r="A3" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="211"/>
-      <c r="C3" s="211"/>
-      <c r="D3" s="211"/>
-      <c r="E3" s="211"/>
-      <c r="F3" s="211"/>
+      <c r="B3" s="236"/>
+      <c r="C3" s="236"/>
+      <c r="D3" s="236"/>
+      <c r="E3" s="236"/>
+      <c r="F3" s="236"/>
       <c r="G3" s="36" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A4" s="212"/>
-      <c r="B4" s="213"/>
-      <c r="C4" s="213"/>
-      <c r="D4" s="213"/>
-      <c r="E4" s="213"/>
-      <c r="F4" s="213"/>
+      <c r="A4" s="237"/>
+      <c r="B4" s="238"/>
+      <c r="C4" s="238"/>
+      <c r="D4" s="238"/>
+      <c r="E4" s="238"/>
+      <c r="F4" s="238"/>
       <c r="G4" s="37" t="s">
         <v>19</v>
       </c>
@@ -6702,80 +6700,80 @@
       <c r="G9" s="66"/>
     </row>
     <row r="10" spans="1:7" ht="85" customHeight="1">
-      <c r="A10" s="222" t="s">
+      <c r="A10" s="230" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="223"/>
-      <c r="C10" s="228" t="s">
+      <c r="B10" s="231"/>
+      <c r="C10" s="221" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="229"/>
-      <c r="E10" s="230"/>
+      <c r="D10" s="222"/>
+      <c r="E10" s="223"/>
       <c r="F10" s="67"/>
       <c r="G10" s="68"/>
     </row>
     <row r="11" spans="1:7" ht="42.5" customHeight="1">
-      <c r="A11" s="224" t="s">
+      <c r="A11" s="232" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="225"/>
-      <c r="C11" s="231" t="s">
+      <c r="B11" s="233"/>
+      <c r="C11" s="224" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="232"/>
-      <c r="E11" s="233"/>
+      <c r="D11" s="225"/>
+      <c r="E11" s="226"/>
       <c r="F11" s="67"/>
       <c r="G11" s="68"/>
     </row>
     <row r="12" spans="1:7" ht="42.5" customHeight="1">
-      <c r="A12" s="224" t="s">
+      <c r="A12" s="232" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="225"/>
-      <c r="C12" s="231" t="s">
+      <c r="B12" s="233"/>
+      <c r="C12" s="224" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="232"/>
-      <c r="E12" s="233"/>
+      <c r="D12" s="225"/>
+      <c r="E12" s="226"/>
       <c r="F12" s="67"/>
       <c r="G12" s="68"/>
     </row>
     <row r="13" spans="1:7" ht="42.5" customHeight="1">
-      <c r="A13" s="224" t="s">
+      <c r="A13" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="225"/>
-      <c r="C13" s="231" t="s">
+      <c r="B13" s="233"/>
+      <c r="C13" s="224" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="232"/>
-      <c r="E13" s="233"/>
+      <c r="D13" s="225"/>
+      <c r="E13" s="226"/>
       <c r="F13" s="67"/>
       <c r="G13" s="68"/>
     </row>
     <row r="14" spans="1:7" ht="42.5" customHeight="1">
-      <c r="A14" s="224" t="s">
+      <c r="A14" s="232" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="225"/>
-      <c r="C14" s="231" t="s">
+      <c r="B14" s="233"/>
+      <c r="C14" s="224" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="232"/>
-      <c r="E14" s="233"/>
+      <c r="D14" s="225"/>
+      <c r="E14" s="226"/>
       <c r="F14" s="67"/>
       <c r="G14" s="68"/>
     </row>
     <row r="15" spans="1:7" ht="85" customHeight="1">
-      <c r="A15" s="226" t="s">
+      <c r="A15" s="219" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="227"/>
-      <c r="C15" s="234" t="s">
+      <c r="B15" s="220"/>
+      <c r="C15" s="227" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="235"/>
-      <c r="E15" s="236"/>
+      <c r="D15" s="228"/>
+      <c r="E15" s="229"/>
       <c r="F15" s="67"/>
       <c r="G15" s="68"/>
     </row>
@@ -6812,11 +6810,11 @@
       <c r="A19" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="237" t="s">
+      <c r="B19" s="213" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="238"/>
-      <c r="D19" s="238"/>
+      <c r="C19" s="214"/>
+      <c r="D19" s="214"/>
       <c r="E19" s="50" t="s">
         <v>35</v>
       </c>
@@ -6827,11 +6825,11 @@
       <c r="A20" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="239" t="s">
+      <c r="B20" s="215" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="240"/>
-      <c r="D20" s="240"/>
+      <c r="C20" s="216"/>
+      <c r="D20" s="216"/>
       <c r="E20" s="52" t="s">
         <v>38</v>
       </c>
@@ -6840,36 +6838,36 @@
     </row>
     <row r="21" spans="1:7" ht="17" customHeight="1">
       <c r="A21" s="53"/>
-      <c r="B21" s="241"/>
-      <c r="C21" s="242"/>
-      <c r="D21" s="242"/>
+      <c r="B21" s="217"/>
+      <c r="C21" s="218"/>
+      <c r="D21" s="218"/>
       <c r="E21" s="54"/>
       <c r="F21" s="72"/>
       <c r="G21" s="73"/>
     </row>
     <row r="22" spans="1:7" ht="17" customHeight="1">
       <c r="A22" s="53"/>
-      <c r="B22" s="241"/>
-      <c r="C22" s="242"/>
-      <c r="D22" s="242"/>
+      <c r="B22" s="217"/>
+      <c r="C22" s="218"/>
+      <c r="D22" s="218"/>
       <c r="E22" s="54"/>
       <c r="F22" s="72"/>
       <c r="G22" s="73"/>
     </row>
     <row r="23" spans="1:7" ht="17" customHeight="1">
       <c r="A23" s="53"/>
-      <c r="B23" s="241"/>
-      <c r="C23" s="242"/>
-      <c r="D23" s="242"/>
+      <c r="B23" s="217"/>
+      <c r="C23" s="218"/>
+      <c r="D23" s="218"/>
       <c r="E23" s="54"/>
       <c r="F23" s="72"/>
       <c r="G23" s="73"/>
     </row>
     <row r="24" spans="1:7" ht="17" customHeight="1">
       <c r="A24" s="55"/>
-      <c r="B24" s="243"/>
-      <c r="C24" s="244"/>
-      <c r="D24" s="244"/>
+      <c r="B24" s="209"/>
+      <c r="C24" s="210"/>
+      <c r="D24" s="210"/>
       <c r="E24" s="56"/>
       <c r="F24" s="72"/>
       <c r="G24" s="73"/>
@@ -6895,15 +6893,15 @@
       <c r="G26" s="74"/>
     </row>
     <row r="27" spans="1:7" ht="107.75" customHeight="1">
-      <c r="A27" s="245" t="s">
+      <c r="A27" s="211" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="246"/>
-      <c r="C27" s="246"/>
-      <c r="D27" s="246"/>
-      <c r="E27" s="246"/>
-      <c r="F27" s="246"/>
-      <c r="G27" s="246"/>
+      <c r="B27" s="212"/>
+      <c r="C27" s="212"/>
+      <c r="D27" s="212"/>
+      <c r="E27" s="212"/>
+      <c r="F27" s="212"/>
+      <c r="G27" s="212"/>
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1">
       <c r="A28" s="57" t="s">
@@ -6917,15 +6915,15 @@
       <c r="G28" s="59"/>
     </row>
     <row r="29" spans="1:7" ht="107.75" customHeight="1">
-      <c r="A29" s="245" t="s">
+      <c r="A29" s="211" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="246"/>
-      <c r="C29" s="246"/>
-      <c r="D29" s="246"/>
-      <c r="E29" s="246"/>
-      <c r="F29" s="246"/>
-      <c r="G29" s="246"/>
+      <c r="B29" s="212"/>
+      <c r="C29" s="212"/>
+      <c r="D29" s="212"/>
+      <c r="E29" s="212"/>
+      <c r="F29" s="212"/>
+      <c r="G29" s="212"/>
     </row>
     <row r="30" spans="1:7" ht="10" customHeight="1">
       <c r="A30" s="8"/>
@@ -6997,7 +6995,7 @@
       <c r="G36" s="14"/>
     </row>
     <row r="37" spans="1:7" ht="28.25" customHeight="1">
-      <c r="A37" s="206" t="s">
+      <c r="A37" s="208" t="s">
         <v>13</v>
       </c>
       <c r="B37" s="193"/>
@@ -7115,11 +7113,11 @@
     </row>
     <row r="51" spans="8:12" ht="120.5" customHeight="1">
       <c r="H51" s="31"/>
-      <c r="I51" s="207" t="s">
+      <c r="I51" s="202" t="s">
         <v>14</v>
       </c>
-      <c r="J51" s="208"/>
-      <c r="K51" s="208"/>
+      <c r="J51" s="203"/>
+      <c r="K51" s="203"/>
       <c r="L51" s="32"/>
     </row>
     <row r="52" spans="8:12" ht="10" customHeight="1">
@@ -7131,33 +7129,33 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F4"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F4"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="B24:D24"/>
   </mergeCells>
   <pageMargins left="0.59055100000000005" right="0.59055100000000005" top="0.39370100000000002" bottom="0.39370100000000002" header="0.19685" footer="0.39370100000000002"/>
   <pageSetup orientation="landscape"/>
@@ -7188,78 +7186,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.25" customHeight="1">
-      <c r="A1" s="249" t="s">
+      <c r="A1" s="256" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="215"/>
-      <c r="C1" s="216"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="F1" s="248"/>
+      <c r="B1" s="240"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="242"/>
+      <c r="F1" s="255"/>
     </row>
     <row r="2" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A2" s="252" t="s">
+      <c r="A2" s="250" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="219"/>
-      <c r="C2" s="219"/>
-      <c r="D2" s="252" t="s">
+      <c r="B2" s="244"/>
+      <c r="C2" s="244"/>
+      <c r="D2" s="250" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="219"/>
-      <c r="F2" s="211"/>
+      <c r="E2" s="244"/>
+      <c r="F2" s="236"/>
     </row>
     <row r="3" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A3" s="253" t="s">
+      <c r="A3" s="251" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="211"/>
-      <c r="C3" s="211"/>
-      <c r="D3" s="253" t="s">
+      <c r="B3" s="236"/>
+      <c r="C3" s="236"/>
+      <c r="D3" s="251" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="211"/>
+      <c r="E3" s="236"/>
       <c r="F3" s="36" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A4" s="254" t="s">
+      <c r="A4" s="252" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="213"/>
-      <c r="C4" s="213"/>
-      <c r="D4" s="254" t="s">
+      <c r="B4" s="238"/>
+      <c r="C4" s="238"/>
+      <c r="D4" s="252" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="213"/>
+      <c r="E4" s="238"/>
       <c r="F4" s="37" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A5" s="255" t="s">
+      <c r="A5" s="253" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="256"/>
-      <c r="C5" s="256"/>
-      <c r="D5" s="256"/>
-      <c r="E5" s="256"/>
+      <c r="B5" s="254"/>
+      <c r="C5" s="254"/>
+      <c r="D5" s="254"/>
+      <c r="E5" s="254"/>
       <c r="F5" s="75" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A6" s="250" t="s">
+      <c r="A6" s="248" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="251"/>
-      <c r="C6" s="251"/>
-      <c r="D6" s="251"/>
-      <c r="E6" s="251"/>
+      <c r="B6" s="249"/>
+      <c r="C6" s="249"/>
+      <c r="D6" s="249"/>
+      <c r="E6" s="249"/>
       <c r="F6" s="76" cm="1">
         <f t="array" aca="1" ref="F6" ca="1">TODAY()</f>
-        <v>45929</v>
+        <v>45936</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="10" customHeight="1">
@@ -7307,76 +7305,76 @@
       <c r="F11" s="44"/>
     </row>
     <row r="12" spans="1:6" ht="85" customHeight="1">
-      <c r="A12" s="222" t="s">
+      <c r="A12" s="230" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="223"/>
-      <c r="C12" s="228" t="s">
+      <c r="B12" s="231"/>
+      <c r="C12" s="221" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="229"/>
-      <c r="E12" s="229"/>
-      <c r="F12" s="230"/>
+      <c r="D12" s="222"/>
+      <c r="E12" s="222"/>
+      <c r="F12" s="223"/>
     </row>
     <row r="13" spans="1:6" ht="42.5" customHeight="1">
-      <c r="A13" s="224" t="s">
+      <c r="A13" s="232" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="225"/>
-      <c r="C13" s="231" t="s">
+      <c r="B13" s="233"/>
+      <c r="C13" s="224" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="232"/>
-      <c r="E13" s="232"/>
-      <c r="F13" s="233"/>
+      <c r="D13" s="225"/>
+      <c r="E13" s="225"/>
+      <c r="F13" s="226"/>
     </row>
     <row r="14" spans="1:6" ht="42.5" customHeight="1">
-      <c r="A14" s="224" t="s">
+      <c r="A14" s="232" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="225"/>
-      <c r="C14" s="231" t="s">
+      <c r="B14" s="233"/>
+      <c r="C14" s="224" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="232"/>
-      <c r="E14" s="232"/>
-      <c r="F14" s="233"/>
+      <c r="D14" s="225"/>
+      <c r="E14" s="225"/>
+      <c r="F14" s="226"/>
     </row>
     <row r="15" spans="1:6" ht="42.5" customHeight="1">
-      <c r="A15" s="224" t="s">
+      <c r="A15" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="225"/>
-      <c r="C15" s="231" t="s">
+      <c r="B15" s="233"/>
+      <c r="C15" s="224" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="232"/>
-      <c r="E15" s="232"/>
-      <c r="F15" s="233"/>
+      <c r="D15" s="225"/>
+      <c r="E15" s="225"/>
+      <c r="F15" s="226"/>
     </row>
     <row r="16" spans="1:6" ht="42.5" customHeight="1">
-      <c r="A16" s="224" t="s">
+      <c r="A16" s="232" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="225"/>
-      <c r="C16" s="231" t="s">
+      <c r="B16" s="233"/>
+      <c r="C16" s="224" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="232"/>
-      <c r="E16" s="232"/>
-      <c r="F16" s="233"/>
+      <c r="D16" s="225"/>
+      <c r="E16" s="225"/>
+      <c r="F16" s="226"/>
     </row>
     <row r="17" spans="1:6" ht="56.75" customHeight="1">
-      <c r="A17" s="226" t="s">
+      <c r="A17" s="219" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="227"/>
-      <c r="C17" s="234" t="s">
+      <c r="B17" s="220"/>
+      <c r="C17" s="227" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="235"/>
-      <c r="E17" s="235"/>
-      <c r="F17" s="236"/>
+      <c r="D17" s="228"/>
+      <c r="E17" s="228"/>
+      <c r="F17" s="229"/>
     </row>
     <row r="18" spans="1:6" ht="10" customHeight="1">
       <c r="A18" s="45"/>
@@ -7416,12 +7414,12 @@
       <c r="A22" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="237" t="s">
+      <c r="B22" s="213" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="238"/>
-      <c r="D22" s="238"/>
-      <c r="E22" s="238"/>
+      <c r="C22" s="214"/>
+      <c r="D22" s="214"/>
+      <c r="E22" s="214"/>
       <c r="F22" s="50" t="s">
         <v>35</v>
       </c>
@@ -7430,46 +7428,46 @@
       <c r="A23" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="239" t="s">
+      <c r="B23" s="215" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="240"/>
-      <c r="D23" s="240"/>
-      <c r="E23" s="240"/>
+      <c r="C23" s="216"/>
+      <c r="D23" s="216"/>
+      <c r="E23" s="216"/>
       <c r="F23" s="52" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="17" customHeight="1">
       <c r="A24" s="53"/>
-      <c r="B24" s="241"/>
-      <c r="C24" s="242"/>
-      <c r="D24" s="242"/>
-      <c r="E24" s="242"/>
+      <c r="B24" s="217"/>
+      <c r="C24" s="218"/>
+      <c r="D24" s="218"/>
+      <c r="E24" s="218"/>
       <c r="F24" s="54"/>
     </row>
     <row r="25" spans="1:6" ht="17" customHeight="1">
       <c r="A25" s="53"/>
-      <c r="B25" s="241"/>
-      <c r="C25" s="242"/>
-      <c r="D25" s="242"/>
-      <c r="E25" s="242"/>
+      <c r="B25" s="217"/>
+      <c r="C25" s="218"/>
+      <c r="D25" s="218"/>
+      <c r="E25" s="218"/>
       <c r="F25" s="54"/>
     </row>
     <row r="26" spans="1:6" ht="17" customHeight="1">
       <c r="A26" s="53"/>
-      <c r="B26" s="241"/>
-      <c r="C26" s="242"/>
-      <c r="D26" s="242"/>
-      <c r="E26" s="242"/>
+      <c r="B26" s="217"/>
+      <c r="C26" s="218"/>
+      <c r="D26" s="218"/>
+      <c r="E26" s="218"/>
       <c r="F26" s="54"/>
     </row>
     <row r="27" spans="1:6" ht="17" customHeight="1">
       <c r="A27" s="55"/>
-      <c r="B27" s="243"/>
-      <c r="C27" s="244"/>
-      <c r="D27" s="244"/>
-      <c r="E27" s="244"/>
+      <c r="B27" s="209"/>
+      <c r="C27" s="210"/>
+      <c r="D27" s="210"/>
+      <c r="E27" s="210"/>
       <c r="F27" s="56"/>
     </row>
     <row r="28" spans="1:6" ht="28.25" customHeight="1">
@@ -7491,14 +7489,14 @@
       <c r="F29" s="59"/>
     </row>
     <row r="30" spans="1:6" ht="224" customHeight="1">
-      <c r="A30" s="245" t="s">
+      <c r="A30" s="211" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="246"/>
-      <c r="C30" s="246"/>
-      <c r="D30" s="246"/>
-      <c r="E30" s="246"/>
-      <c r="F30" s="246"/>
+      <c r="B30" s="212"/>
+      <c r="C30" s="212"/>
+      <c r="D30" s="212"/>
+      <c r="E30" s="212"/>
+      <c r="F30" s="212"/>
     </row>
     <row r="31" spans="1:6" ht="14.25" customHeight="1">
       <c r="A31" s="57" t="s">
@@ -7511,14 +7509,14 @@
       <c r="F31" s="59"/>
     </row>
     <row r="32" spans="1:6" ht="224" customHeight="1">
-      <c r="A32" s="245" t="s">
+      <c r="A32" s="211" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="246"/>
-      <c r="C32" s="246"/>
-      <c r="D32" s="246"/>
-      <c r="E32" s="246"/>
-      <c r="F32" s="246"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="212"/>
+      <c r="D32" s="212"/>
+      <c r="E32" s="212"/>
+      <c r="F32" s="212"/>
     </row>
     <row r="33" spans="1:6" ht="10" customHeight="1">
       <c r="A33" s="8"/>
@@ -7583,7 +7581,7 @@
       <c r="F39" s="14"/>
     </row>
     <row r="40" spans="1:6" ht="28.25" customHeight="1">
-      <c r="A40" s="206" t="s">
+      <c r="A40" s="208" t="s">
         <v>13</v>
       </c>
       <c r="B40" s="193"/>
@@ -7697,11 +7695,11 @@
     </row>
     <row r="55" spans="1:11" ht="120.5" customHeight="1">
       <c r="G55" s="31"/>
-      <c r="H55" s="207" t="s">
+      <c r="H55" s="202" t="s">
         <v>14</v>
       </c>
-      <c r="I55" s="208"/>
-      <c r="J55" s="208"/>
+      <c r="I55" s="203"/>
+      <c r="J55" s="203"/>
       <c r="K55" s="32"/>
     </row>
     <row r="56" spans="1:11" ht="10" customHeight="1">
@@ -7713,24 +7711,11 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A16:B16"/>
@@ -7741,11 +7726,24 @@
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.59055100000000005" right="0.59055100000000005" top="0.39370100000000002" bottom="0.39370100000000002" header="0.19685" footer="0.39370100000000002"/>
   <pageSetup orientation="portrait"/>
@@ -7781,87 +7779,87 @@
       <c r="A1" s="257" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="217"/>
-      <c r="C1" s="217"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="F1" s="217"/>
-      <c r="G1" s="217"/>
-      <c r="H1" s="248"/>
+      <c r="B1" s="242"/>
+      <c r="C1" s="242"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="242"/>
+      <c r="F1" s="242"/>
+      <c r="G1" s="242"/>
+      <c r="H1" s="255"/>
     </row>
     <row r="2" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A2" s="252" t="s">
+      <c r="A2" s="250" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="219"/>
-      <c r="C2" s="219"/>
-      <c r="D2" s="219"/>
-      <c r="E2" s="252" t="s">
+      <c r="B2" s="244"/>
+      <c r="C2" s="244"/>
+      <c r="D2" s="244"/>
+      <c r="E2" s="250" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="219"/>
-      <c r="G2" s="219"/>
-      <c r="H2" s="211"/>
+      <c r="F2" s="244"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="236"/>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A3" s="253" t="s">
+      <c r="A3" s="251" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="211"/>
-      <c r="C3" s="211"/>
-      <c r="D3" s="211"/>
-      <c r="E3" s="253" t="s">
+      <c r="B3" s="236"/>
+      <c r="C3" s="236"/>
+      <c r="D3" s="236"/>
+      <c r="E3" s="251" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="211"/>
-      <c r="G3" s="211"/>
+      <c r="F3" s="236"/>
+      <c r="G3" s="236"/>
       <c r="H3" s="36" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A4" s="254" t="s">
+      <c r="A4" s="252" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="213"/>
-      <c r="C4" s="213"/>
-      <c r="D4" s="213"/>
-      <c r="E4" s="254" t="s">
+      <c r="B4" s="238"/>
+      <c r="C4" s="238"/>
+      <c r="D4" s="238"/>
+      <c r="E4" s="252" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="213"/>
-      <c r="G4" s="213"/>
+      <c r="F4" s="238"/>
+      <c r="G4" s="238"/>
       <c r="H4" s="37" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A5" s="255" t="s">
+      <c r="A5" s="253" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="256"/>
-      <c r="C5" s="256"/>
-      <c r="D5" s="256"/>
-      <c r="E5" s="256"/>
-      <c r="F5" s="256"/>
-      <c r="G5" s="256"/>
+      <c r="B5" s="254"/>
+      <c r="C5" s="254"/>
+      <c r="D5" s="254"/>
+      <c r="E5" s="254"/>
+      <c r="F5" s="254"/>
+      <c r="G5" s="254"/>
       <c r="H5" s="75" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A6" s="250" t="s">
+      <c r="A6" s="248" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="251"/>
-      <c r="C6" s="251"/>
-      <c r="D6" s="251"/>
-      <c r="E6" s="251"/>
-      <c r="F6" s="251"/>
-      <c r="G6" s="251"/>
+      <c r="B6" s="249"/>
+      <c r="C6" s="249"/>
+      <c r="D6" s="249"/>
+      <c r="E6" s="249"/>
+      <c r="F6" s="249"/>
+      <c r="G6" s="249"/>
       <c r="H6" s="76" cm="1">
         <f t="array" aca="1" ref="H6" ca="1">TODAY()</f>
-        <v>45929</v>
+        <v>45936</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="10" customHeight="1">
@@ -7929,86 +7927,86 @@
       <c r="H12" s="66"/>
     </row>
     <row r="13" spans="1:8" ht="85" customHeight="1">
-      <c r="A13" s="222" t="s">
+      <c r="A13" s="230" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="223"/>
-      <c r="C13" s="228" t="s">
+      <c r="B13" s="231"/>
+      <c r="C13" s="221" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="229"/>
-      <c r="E13" s="229"/>
-      <c r="F13" s="230"/>
+      <c r="D13" s="222"/>
+      <c r="E13" s="222"/>
+      <c r="F13" s="223"/>
       <c r="G13" s="67"/>
       <c r="H13" s="68"/>
     </row>
     <row r="14" spans="1:8" ht="42.5" customHeight="1">
-      <c r="A14" s="224" t="s">
+      <c r="A14" s="232" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="225"/>
-      <c r="C14" s="231" t="s">
+      <c r="B14" s="233"/>
+      <c r="C14" s="224" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="232"/>
-      <c r="E14" s="232"/>
-      <c r="F14" s="233"/>
+      <c r="D14" s="225"/>
+      <c r="E14" s="225"/>
+      <c r="F14" s="226"/>
       <c r="G14" s="67"/>
       <c r="H14" s="68"/>
     </row>
     <row r="15" spans="1:8" ht="42.5" customHeight="1">
-      <c r="A15" s="224" t="s">
+      <c r="A15" s="232" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="225"/>
-      <c r="C15" s="231" t="s">
+      <c r="B15" s="233"/>
+      <c r="C15" s="224" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="232"/>
-      <c r="E15" s="232"/>
-      <c r="F15" s="233"/>
+      <c r="D15" s="225"/>
+      <c r="E15" s="225"/>
+      <c r="F15" s="226"/>
       <c r="G15" s="67"/>
       <c r="H15" s="68"/>
     </row>
     <row r="16" spans="1:8" ht="42.5" customHeight="1">
-      <c r="A16" s="224" t="s">
+      <c r="A16" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="225"/>
-      <c r="C16" s="231" t="s">
+      <c r="B16" s="233"/>
+      <c r="C16" s="224" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="232"/>
-      <c r="E16" s="232"/>
-      <c r="F16" s="233"/>
+      <c r="D16" s="225"/>
+      <c r="E16" s="225"/>
+      <c r="F16" s="226"/>
       <c r="G16" s="67"/>
       <c r="H16" s="68"/>
     </row>
     <row r="17" spans="1:8" ht="42.5" customHeight="1">
-      <c r="A17" s="224" t="s">
+      <c r="A17" s="232" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="225"/>
-      <c r="C17" s="231" t="s">
+      <c r="B17" s="233"/>
+      <c r="C17" s="224" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="232"/>
-      <c r="E17" s="232"/>
-      <c r="F17" s="233"/>
+      <c r="D17" s="225"/>
+      <c r="E17" s="225"/>
+      <c r="F17" s="226"/>
       <c r="G17" s="67"/>
       <c r="H17" s="68"/>
     </row>
     <row r="18" spans="1:8" ht="85" customHeight="1">
-      <c r="A18" s="226" t="s">
+      <c r="A18" s="219" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="227"/>
-      <c r="C18" s="234" t="s">
+      <c r="B18" s="220"/>
+      <c r="C18" s="227" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="235"/>
-      <c r="E18" s="235"/>
-      <c r="F18" s="236"/>
+      <c r="D18" s="228"/>
+      <c r="E18" s="228"/>
+      <c r="F18" s="229"/>
       <c r="G18" s="67"/>
       <c r="H18" s="68"/>
     </row>
@@ -8058,12 +8056,12 @@
       <c r="A23" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="237" t="s">
+      <c r="B23" s="213" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="238"/>
-      <c r="D23" s="238"/>
-      <c r="E23" s="238"/>
+      <c r="C23" s="214"/>
+      <c r="D23" s="214"/>
+      <c r="E23" s="214"/>
       <c r="F23" s="50" t="s">
         <v>35</v>
       </c>
@@ -8074,12 +8072,12 @@
       <c r="A24" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="239" t="s">
+      <c r="B24" s="215" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="240"/>
-      <c r="D24" s="240"/>
-      <c r="E24" s="240"/>
+      <c r="C24" s="216"/>
+      <c r="D24" s="216"/>
+      <c r="E24" s="216"/>
       <c r="F24" s="52" t="s">
         <v>38</v>
       </c>
@@ -8088,40 +8086,40 @@
     </row>
     <row r="25" spans="1:8" ht="17" customHeight="1">
       <c r="A25" s="53"/>
-      <c r="B25" s="241"/>
-      <c r="C25" s="242"/>
-      <c r="D25" s="242"/>
-      <c r="E25" s="242"/>
+      <c r="B25" s="217"/>
+      <c r="C25" s="218"/>
+      <c r="D25" s="218"/>
+      <c r="E25" s="218"/>
       <c r="F25" s="54"/>
       <c r="G25" s="72"/>
       <c r="H25" s="73"/>
     </row>
     <row r="26" spans="1:8" ht="17" customHeight="1">
       <c r="A26" s="53"/>
-      <c r="B26" s="241"/>
-      <c r="C26" s="242"/>
-      <c r="D26" s="242"/>
-      <c r="E26" s="242"/>
+      <c r="B26" s="217"/>
+      <c r="C26" s="218"/>
+      <c r="D26" s="218"/>
+      <c r="E26" s="218"/>
       <c r="F26" s="54"/>
       <c r="G26" s="72"/>
       <c r="H26" s="73"/>
     </row>
     <row r="27" spans="1:8" ht="17" customHeight="1">
       <c r="A27" s="53"/>
-      <c r="B27" s="241"/>
-      <c r="C27" s="242"/>
-      <c r="D27" s="242"/>
-      <c r="E27" s="242"/>
+      <c r="B27" s="217"/>
+      <c r="C27" s="218"/>
+      <c r="D27" s="218"/>
+      <c r="E27" s="218"/>
       <c r="F27" s="54"/>
       <c r="G27" s="72"/>
       <c r="H27" s="73"/>
     </row>
     <row r="28" spans="1:8" ht="17" customHeight="1">
       <c r="A28" s="55"/>
-      <c r="B28" s="243"/>
-      <c r="C28" s="244"/>
-      <c r="D28" s="244"/>
-      <c r="E28" s="244"/>
+      <c r="B28" s="209"/>
+      <c r="C28" s="210"/>
+      <c r="D28" s="210"/>
+      <c r="E28" s="210"/>
       <c r="F28" s="56"/>
       <c r="G28" s="72"/>
       <c r="H28" s="73"/>
@@ -8149,16 +8147,16 @@
       <c r="H30" s="74"/>
     </row>
     <row r="31" spans="1:8" ht="110.5" customHeight="1">
-      <c r="A31" s="245" t="s">
+      <c r="A31" s="211" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="246"/>
-      <c r="C31" s="246"/>
-      <c r="D31" s="246"/>
-      <c r="E31" s="246"/>
-      <c r="F31" s="246"/>
-      <c r="G31" s="246"/>
-      <c r="H31" s="246"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="212"/>
+      <c r="D31" s="212"/>
+      <c r="E31" s="212"/>
+      <c r="F31" s="212"/>
+      <c r="G31" s="212"/>
+      <c r="H31" s="212"/>
     </row>
     <row r="32" spans="1:8" ht="14.25" customHeight="1">
       <c r="A32" s="57" t="s">
@@ -8173,16 +8171,16 @@
       <c r="H32" s="59"/>
     </row>
     <row r="33" spans="1:8" ht="110.5" customHeight="1">
-      <c r="A33" s="245" t="s">
+      <c r="A33" s="211" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="246"/>
-      <c r="C33" s="246"/>
-      <c r="D33" s="246"/>
-      <c r="E33" s="246"/>
-      <c r="F33" s="246"/>
-      <c r="G33" s="246"/>
-      <c r="H33" s="246"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="212"/>
+      <c r="D33" s="212"/>
+      <c r="E33" s="212"/>
+      <c r="F33" s="212"/>
+      <c r="G33" s="212"/>
+      <c r="H33" s="212"/>
     </row>
     <row r="34" spans="1:8" ht="10" customHeight="1">
       <c r="A34" s="8"/>
@@ -8261,7 +8259,7 @@
       <c r="H40" s="14"/>
     </row>
     <row r="41" spans="1:8" ht="28.25" customHeight="1">
-      <c r="A41" s="206" t="s">
+      <c r="A41" s="208" t="s">
         <v>13</v>
       </c>
       <c r="B41" s="193"/>
@@ -8401,11 +8399,11 @@
     </row>
     <row r="56" spans="1:13" ht="120.5" customHeight="1">
       <c r="I56" s="31"/>
-      <c r="J56" s="207" t="s">
+      <c r="J56" s="202" t="s">
         <v>14</v>
       </c>
-      <c r="K56" s="208"/>
-      <c r="L56" s="208"/>
+      <c r="K56" s="203"/>
+      <c r="L56" s="203"/>
       <c r="M56" s="32"/>
     </row>
     <row r="57" spans="1:13" ht="10" customHeight="1">
@@ -8417,24 +8415,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
@@ -8450,6 +8430,24 @@
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="B28:E28"/>
   </mergeCells>
   <pageMargins left="0.59055100000000005" right="0.59055100000000005" top="0.39370100000000002" bottom="0.39370100000000002" header="0.19685" footer="0.39370100000000002"/>
   <pageSetup orientation="landscape"/>
